--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136044486</v>
       </c>
       <c r="B3" t="n">
-        <v>87584</v>
+        <v>87586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92123</v>
+        <v>92126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 32500-2026 artfynd.xlsx
+++ b/artfynd/A 32500-2026 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>136043920</v>
       </c>
       <c r="B4" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>136044723</v>
       </c>
       <c r="B5" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
